--- a/data/calc.xlsx
+++ b/data/calc.xlsx
@@ -1,34 +1,92 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\DS\lessons\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\lessons\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2A4D69-2BA9-49A3-B8F2-48310D9C4110}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D65347A9-99CF-44B7-A716-5D760EF4EBEE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="432" yWindow="-21168" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-10995" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t>Обследование объекта и разработка ТЗ</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Инфраструктура</t>
   </si>
   <si>
-    <t>Работы</t>
+    <t>УБТ</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Пусконаладочные работы:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+ПНР вновь смонтированного  полевого оборудования
+ПНР аппаратной части вновь вводимых каналов АСУТП
+Участие в комплексных испытаниях в части обеспечения работы вновь смонтированного полевого оборудования
+Устранение замечаний по результатам опытной эксплуатации</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>Проектно-изыскательные работы:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">
+Предпроектное обследование
+Разработка комплекта рабочей документации</t>
+    </r>
   </si>
   <si>
     <t>Ромашка 1</t>
@@ -44,10 +102,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -56,20 +115,50 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -80,7 +169,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -88,16 +177,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -401,44 +518,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="73.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.33203125" customWidth="1"/>
-    <col min="3" max="3" width="15.5546875" customWidth="1"/>
+    <col min="1" max="1" width="48.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="42" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="5">
+        <v>5398200</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="3" spans="1:5" ht="130.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="B3" s="7">
+        <v>3100000</v>
+      </c>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3">
-        <v>6545760</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B3" s="1"/>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B4" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>